--- a/Data/EXCEL/Transfer/salemon/202208/6683-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/6683-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DF7483C-504B-455B-99A8-70F816131884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{637EEA1F-7516-485B-872A-23C205BFB269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="6683-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,23 +1227,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
-    <col min="9" max="9" width="9.625" customWidth="1"/>
-    <col min="10" max="11" width="10.25" customWidth="1"/>
-    <col min="12" max="12" width="8.625" customWidth="1"/>
-    <col min="13" max="13" width="10.25" customWidth="1"/>
-    <col min="14" max="14" width="9.625" customWidth="1"/>
-    <col min="15" max="16" width="10.25" customWidth="1"/>
-    <col min="17" max="17" width="9" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="14.125" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +1270,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1301,7 +1309,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1344,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1383,7 +1391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1436,7 +1444,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1489,7 +1497,7 @@
         <v>4.6100000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1542,7 +1550,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1648,7 +1656,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1701,7 +1709,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1754,7 +1762,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1807,7 +1815,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1860,7 +1868,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1913,7 +1921,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1966,7 +1974,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2019,7 +2027,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2072,7 +2080,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2125,7 +2133,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2178,7 +2186,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2231,7 +2239,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2284,7 +2292,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2337,7 +2345,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2390,7 +2398,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2443,7 +2451,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2496,7 +2504,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2549,7 +2557,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2602,7 +2610,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2655,7 +2663,7 @@
         <v>44.1</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2708,7 +2716,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2761,7 +2769,7 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2814,7 +2822,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2867,7 +2875,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2920,7 +2928,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2973,7 +2981,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3026,7 +3034,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3079,7 +3087,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3132,7 +3140,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3185,7 +3193,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3238,7 +3246,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3291,7 +3299,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3344,7 +3352,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3397,7 +3405,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3450,7 +3458,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3503,7 +3511,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3556,7 +3564,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3609,7 +3617,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3662,7 +3670,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3715,7 +3723,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3768,7 +3776,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3821,7 +3829,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3874,7 +3882,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3927,7 +3935,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3980,7 +3988,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4033,7 +4041,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4086,7 +4094,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4139,7 +4147,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4207,7 +4215,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>